--- a/ACL_закупки_2026.xlsx
+++ b/ACL_закупки_2026.xlsx
@@ -512,18 +512,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -563,25 +564,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Позиции HemosIL / целевая позиция</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>НМЦК / Сумма контракта, руб.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Дата размещения</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Победитель / Поставщик</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Срок исполнения контракта</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -608,27 +614,32 @@
           <t>ГБУЗ «Городская клиническая больница им. В.В. Вересаева ДЗМ» (г. Москва, ул. Лобненская, д. 10)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>HemosIL Rinse Solution / Буферный промывающий раствор ИВД</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2 793 000</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>16.03.2026</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Не раскрыт (данные скрыты на площадке)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Буферный промывающий раствор ИВД, 200 шт. × 13 965 руб. Протокол подведения итогов — 06.04.2026. Аукцион в электронной форме.</t>
         </is>
@@ -655,27 +666,32 @@
           <t>БУЗ ВО «Воронежская областная клиническая больница №1» (г. Воронеж, Московский пр-кт, д. 151)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Cleaning Solution / Cleaning Agent</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>1 497 473</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Не раскрыт (данные скрыты на площадке)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Моющий/чистящий раствор ИВД 15 шт. (3 026,36 руб./шт.), 24 шт. (6 917,40 руб./шт.), 32 шт. (25 292,89 руб./шт.). Заказчик: БУЗ ВО ВОКБ №1. Организатор: Министерство по регулированию контрактной системы Воронежской области. Протокол — 08.06.2026.</t>
         </is>
@@ -702,27 +718,32 @@
           <t>ФГБУ «Федеральный клинический центр высоких медицинских технологий ФМБА России» (Московская обл., г. Химки, мкр. Новогорск)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>HemosIL Rinse Solution; HemosIL Cleaning Agent; HemosIL Wash-R Emulsion</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1 500 000</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>21.04.2026</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>ООО «Герда Мед» (ИНН 7709975306, г. Москва, 3-й Сыромятнический пер., д. 3/9, стр. 6)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Буферный промывающий раствор ИВД (11 255,24 руб.), специальный моющий раствор для деконтаминации игл (2 820,99 руб.), оптический референс/промывающая жидкость (12 067,80 руб.) и др. реагенты ACL. Площадка: РТС-тендер.</t>
         </is>
@@ -749,27 +770,32 @@
           <t>Не указан в открытых источниках (Воронежская область, организатор — Министерство по регулированию контрактной системы Воронежской области)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Rinse Solution / Буферный промывающий раствор ИВД</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>859 687 (НМЦК: 720 276,48 — по позиции «буферный промывающий раствор»; итого по закупке)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>19.06.2026</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Не раскрыт (данные скрыты на площадке)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Буферный промывающий раствор ИВД для ACL-TOP-550 закрытого типа — 1 шт. × 720 276,48 руб. Объём флакона ≥ 4 000 мл.</t>
         </is>
@@ -796,27 +822,32 @@
           <t>ФГБУ «Российский научно-исследовательский институт гематологии и трансфузиологии ФМБА России» (ФГБУ РосНИИГТ ФМБА России)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Нужна детализация по лотам; по описанию включены промывающие/моющие позиции ACL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Лот 3: 1 441 900 | Лот 4: 1 473 916 | Лот 6: 1 042 268 | Лот 7: 858 687 | Лот 10: 1 489 560</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Апрель — май 2026</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>ООО «Торгвита» (ИНН 7801356724)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контрактов)</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Несколько лотов, включающих расходные материалы (в т.ч. промывающие/моющие растворы) для анализаторов ACL Top Instrumentation Laboratory. Дата заключения контрактов: лот 3 — 17.04.2026, лот 10 — 20.04.2026, лот 6 — 20.04.2026, лот 7 — 28.04.2026, лот 4 — 05.05.2026.</t>
         </is>
@@ -843,27 +874,32 @@
           <t>ГБУЗ ПО «Детская областная клиническая больница» (Пензенская область)</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>По открытым данным — реагенты ACL, требуется уточнение конкретной позиции</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>341 319</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Май 2026</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ООО «Лабтэкдиагностика» (ИНН 7825463740, г. Санкт-Петербург)</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Реагенты для коагулометра серии ACL, в т.ч. промывающий/моющий раствор. Дата заключения контракта — 18.05.2026.</t>
         </is>
@@ -890,27 +926,32 @@
           <t>ФГБОУ ВО «Первый Санкт-Петербургский государственный медицинский университет им. И.П. Павлова» Минздрава России</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>По открытым данным — реагенты ACL, требуется уточнение конкретной позиции</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>945 802</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Апрель 2026</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>ООО «Лабтэкдиагностика» (ИНН 7825463740, г. Санкт-Петербург)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Реагенты для коагулологических исследований на анализаторах серии ACL (включая промывающие растворы). Дата заключения контракта — 27.04.2026.</t>
         </is>
@@ -937,36 +978,353 @@
           <t>ГБУЗ «Госпиталь ветеранов войн № 1 Департамента здравоохранения г. Москвы» (ГВВ № 1 ДЗМ)</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Cleaning Solution / Моющий раствор</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>506 067</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>24.04.2026</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Не раскрыт (данные скрыты на площадке)</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>до 31.12.2026 (по условиям контракта)</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Включает моющий/чистящий раствор ИВД для автоматических систем (ACL ELITE PRO). Электронный аукцион.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>0373200069626000113</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Электронный аукцион на поставку моющего/чистящего раствора для работы на анализаторах ACL для нужд ГБУЗ «МНПЦЛИ ДЗМ»</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Московский научно-практический центр лабораторных исследований Департамента здравоохранения города Москвы»</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>HemosIL Cleaning Solution / Моющий раствор</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>772 380</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Не раскрыт (данные скрыты на площадке)</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>до 31.12.2026 (по условиям контракта)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Закупка непосредственно по моющему/чистящему раствору для анализаторов ACL. Количество: 700 шт. × 1 103,40 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>MOSREG3695270</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Раствор моющий HemosIL Cleaning Solution, 00009831700</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Городская клиническая больница № 67 им. Л. А. Ворохобова ДЗМ»</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Cleaning Solution</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>156 653</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Не раскрыт</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>не указан в открытом источнике</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Прямая закупка по наименованию HemosIL Cleaning Solution, код изделия 00009831700.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>0818500000826004115</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Поставка реагентов для клинико-диагностической лаборатории (для анализатора серии ACL)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ЛПУ не раскрыто в краткой карточке агрегатора</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>HemosIL Cleaning Agent; HemosIL Cleaning Solution</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1 215 358</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Июнь 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Не раскрыт</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>до 31.12.2026 (типовой срок, требует проверки по контракту)</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Содержит две целевые позиции: обеззараживающий раствор с гипохлоритом натрия для ACL (170 шт. × 931,34 руб.) и очищающий раствор с 0,5% соляной кислоты для ACL (150 шт. × 2 207,34 руб.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>0818500000826004122</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий для клинико-диагностической лаборатории на автоматический коагулометр серии ACL ТОР</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ЛПУ не раскрыто в краткой карточке агрегатора</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Rinse Solution; HemosIL Cleaning Agent</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>2 979 001</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Июнь 2026</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Не раскрыт</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>до 31.12.2026 (типовой срок, требует проверки по контракту)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Содержит буферный промывающий раствор для ACL TOP (170 шт. × 14 762 руб.) и обеззараживающий раствор с гипохлоритом натрия для ACL (55 шт. × 1 375 руб.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>0372200105026000430</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Поставка реагентов для КДЛ №5</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Заказчик из Санкт-Петербурга, полное наименование требует уточнения по карточке ЕИС</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>HemosIL Rinse Solution; HemosIL Cleaning Agent</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>не полностью раскрыта в сниппете</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Июнь 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Не раскрыт</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>требует уточнения</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>В карточке явно указаны: щелочной буферный промывающий раствор для ACL (на основе ПАВ и консерванта) и «Моющий агент» на основе гипохлорита натрия для коагулометров серии ACL Instrumentation Laboratory (Werfen).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>0373100078726000414</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Поставка наборов реагентов и расходных материалов для исследования гемостаза для ACL TOP и гормонов (Эббот), лот 3</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Заказчик требует уточнения по полной карточке закупки</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>HemosIL Wash-R Emulsion; HemosIL Cleaning Solution</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>по позициям: 66 660 + 12 796,60</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Июнь 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Не раскрыт</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>требует уточнения</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Содержит референсную эмульсию R для ACL (10 шт. × 6 666 руб.) и моющий/чистящий раствор для ACL (10 шт. × 1 279,66 руб.).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1004,7 +1362,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2. Включены закупки, содержащие позиции «Буферный промывающий раствор ИВД», «Моющий/чистящий раствор ИВД» (КТРУ 21.20.23.110/111), предназначенные для коагулометров серии ACL.</t>
+          <t>2. Таблица дополнена закупками, где прямо указаны целевые позиции: HemosIL Cleaning Solution, HemosIL Cleaning Agent, HemosIL Rinse Solution и HemosIL Wash-R Emulsion для коагулометров серии ACL.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1383,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>5. Коагулометры серии ACL производятся компанией Instrumentation Laboratory (Werfen, Италия/США). Промывающие растворы — HemosIL Cleaning Solution / Reference Wash Emulsion.</t>
+          <t>5. Коагулометры серии ACL производятся компанией Instrumentation Laboratory (Werfen, Италия/США). Целевые позиции в этой выгрузке: HemosIL Cleaning Solution, HemosIL Cleaning Agent, HemosIL Rinse Solution, HemosIL Wash-R Emulsion.</t>
         </is>
       </c>
     </row>
